--- a/Knight_Impact_Partners_Grant_Ap2025-11-28_03_31_24 AM Mapping Data Sheet.xlsx
+++ b/Knight_Impact_Partners_Grant_Ap2025-11-28_03_31_24 AM Mapping Data Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarkARodriguez\Documents\Personal\KIP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adityamandal/Desktop/revampedmap/knight-impact-map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ABCF67C-79EF-4F94-B20E-E7AB637887CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948EB46B-1ED6-204D-81C2-5B2CD4C4F520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KIP Grants" sheetId="1" r:id="rId1"/>
@@ -7677,9 +7677,6 @@
     <t>Aligned pooled emergency response funds</t>
   </si>
   <si>
-    <t>Lakeview, South Side</t>
-  </si>
-  <si>
     <t>Crossroads Fund</t>
   </si>
   <si>
@@ -7831,6 +7828,9 @@
   </si>
   <si>
     <t xml:space="preserve">Capacity Building </t>
+  </si>
+  <si>
+    <t>Lakeview</t>
   </si>
 </sst>
 </file>
@@ -7839,7 +7839,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -7852,11 +7852,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -7963,7 +7965,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -7977,11 +7979,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -7997,8 +7996,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8024,6 +8021,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -8360,26 +8358,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BR81"/>
-  <sheetFormatPr defaultRowHeight="42.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="42.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="29" width="25" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="12.08203125" customWidth="1"/>
+    <col min="30" max="30" width="12" customWidth="1"/>
     <col min="31" max="31" width="25" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="27.75" customWidth="1"/>
+    <col min="32" max="32" width="27.6640625" customWidth="1"/>
     <col min="33" max="63" width="25" hidden="1" customWidth="1"/>
     <col min="64" max="64" width="32" customWidth="1"/>
     <col min="65" max="65" width="25" hidden="1" customWidth="1"/>
     <col min="66" max="66" width="25" customWidth="1"/>
-    <col min="67" max="67" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="15.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="25" customWidth="1"/>
-    <col min="69" max="69" width="13.08203125" customWidth="1"/>
+    <col min="69" max="69" width="13" customWidth="1"/>
     <col min="70" max="70" width="9" customWidth="1"/>
     <col min="71" max="1000" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8578,20 +8576,20 @@
       <c r="BN1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BO1" s="9" t="s">
+      <c r="BO1" s="8" t="s">
         <v>1527</v>
       </c>
       <c r="BP1" s="4" t="s">
         <v>1534</v>
       </c>
-      <c r="BQ1" s="13" t="s">
+      <c r="BQ1" s="12" t="s">
         <v>1541</v>
       </c>
-      <c r="BR1" s="13" t="s">
-        <v>1579</v>
+      <c r="BR1" s="12" t="s">
+        <v>1578</v>
       </c>
     </row>
-    <row r="2" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -8751,17 +8749,17 @@
       <c r="BN2" t="s">
         <v>1517</v>
       </c>
-      <c r="BO2" s="6">
+      <c r="BO2" s="5">
         <v>150000</v>
       </c>
       <c r="BP2" t="s">
         <v>1536</v>
       </c>
-      <c r="BR2" s="8" t="s">
-        <v>1585</v>
+      <c r="BR2" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="3" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -8891,23 +8889,23 @@
       <c r="BN3" t="s">
         <v>1517</v>
       </c>
-      <c r="BO3" s="6">
+      <c r="BO3" s="5">
         <v>75000</v>
       </c>
-      <c r="BP3" s="8" t="s">
+      <c r="BP3" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BR3" s="8" t="s">
-        <v>1580</v>
+      <c r="BR3" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="4" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="8" t="s">
-        <v>1572</v>
+    <row r="4" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="7" t="s">
+        <v>1571</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
-      <c r="AF4" s="8" t="s">
+      <c r="AF4" s="7" t="s">
         <v>150</v>
       </c>
       <c r="AG4" s="2"/>
@@ -8920,21 +8918,21 @@
       <c r="BD4" s="2"/>
       <c r="BG4" s="2"/>
       <c r="BI4" s="2"/>
-      <c r="BN4" s="8" t="s">
+      <c r="BN4" s="7" t="s">
         <v>1517</v>
       </c>
-      <c r="BO4" s="6">
+      <c r="BO4" s="5">
         <v>50000</v>
       </c>
-      <c r="BP4" s="8" t="s">
+      <c r="BP4" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR4" s="8" t="s">
-        <v>1595</v>
+      <c r="BR4" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="5" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="10" t="s">
+    <row r="5" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="9" t="s">
         <v>1555</v>
       </c>
       <c r="Y5" s="2"/>
@@ -8942,7 +8940,7 @@
       <c r="AD5" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="AF5" s="8" t="s">
+      <c r="AF5" s="7" t="s">
         <v>537</v>
       </c>
       <c r="AG5" s="2"/>
@@ -8955,23 +8953,23 @@
       <c r="BD5" s="2"/>
       <c r="BG5" s="2"/>
       <c r="BI5" s="2"/>
-      <c r="BN5" s="8" t="s">
+      <c r="BN5" s="7" t="s">
         <v>1517</v>
       </c>
-      <c r="BO5" s="6">
+      <c r="BO5" s="5">
         <v>100000</v>
       </c>
-      <c r="BP5" s="8" t="s">
+      <c r="BP5" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BQ5" s="8" t="s">
+      <c r="BQ5" s="7" t="s">
         <v>1541</v>
       </c>
-      <c r="BR5" s="8" t="s">
-        <v>1582</v>
+      <c r="BR5" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="6" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -9122,17 +9120,17 @@
       <c r="BN6" t="s">
         <v>291</v>
       </c>
-      <c r="BO6" s="6">
+      <c r="BO6" s="5">
         <v>150000</v>
       </c>
-      <c r="BP6" s="8" t="s">
+      <c r="BP6" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR6" s="8" t="s">
-        <v>1580</v>
+      <c r="BR6" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="7" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>122</v>
       </c>
@@ -9280,17 +9278,17 @@
       <c r="BN7" t="s">
         <v>121</v>
       </c>
-      <c r="BO7" s="6">
+      <c r="BO7" s="5">
         <v>175000</v>
       </c>
-      <c r="BP7" s="8" t="s">
+      <c r="BP7" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR7" s="8" t="s">
-        <v>1580</v>
+      <c r="BR7" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="8" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -9447,199 +9445,199 @@
       <c r="BN8" s="3" t="s">
         <v>1524</v>
       </c>
-      <c r="BO8" s="6">
+      <c r="BO8" s="5">
         <v>50000</v>
       </c>
-      <c r="BP8" s="8" t="s">
+      <c r="BP8" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR8" s="8" t="s">
-        <v>1586</v>
+      <c r="BR8" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="9" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>122</v>
       </c>
       <c r="B9" t="s">
         <v>250</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="O9" s="18" t="s">
+      <c r="O9" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="P9" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="Q9" s="18" t="s">
+      <c r="Q9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="R9" s="18" t="s">
+      <c r="R9" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="S9" s="18" t="s">
+      <c r="S9" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="T9" s="18" t="s">
+      <c r="T9" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="U9" s="18" t="s">
+      <c r="U9" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="V9" s="18" t="s">
+      <c r="V9" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="W9" s="18" t="s">
+      <c r="W9" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="X9" s="18" t="s">
+      <c r="X9" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="Y9" s="19" t="s">
+      <c r="Y9" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="Z9" s="19" t="s">
+      <c r="Z9" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="AA9" s="18" t="s">
+      <c r="AA9" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AB9" s="18" t="s">
+      <c r="AB9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="AC9" s="18" t="s">
+      <c r="AC9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="AD9" s="19" t="s">
+      <c r="AD9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="AE9" s="18" t="s">
+      <c r="AE9" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="AF9" s="18" t="s">
+      <c r="AF9" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AG9" s="19" t="s">
+      <c r="AG9" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AH9" s="19" t="s">
+      <c r="AH9" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AI9" s="19" t="s">
+      <c r="AI9" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="AJ9" s="19" t="s">
+      <c r="AJ9" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="AK9" s="19" t="s">
+      <c r="AK9" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="AL9" s="19" t="s">
+      <c r="AL9" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="AM9" s="19" t="s">
+      <c r="AM9" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="AN9" s="19" t="s">
+      <c r="AN9" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="AO9" s="18" t="s">
+      <c r="AO9" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="AP9" s="18"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="18"/>
-      <c r="AS9" s="18"/>
-      <c r="AT9" s="18"/>
-      <c r="AU9" s="18"/>
-      <c r="AV9" s="18"/>
-      <c r="AW9" s="18"/>
-      <c r="AX9" s="18"/>
-      <c r="AY9" s="18"/>
-      <c r="AZ9" s="18"/>
-      <c r="BA9" s="18"/>
-      <c r="BB9" s="18"/>
-      <c r="BC9" s="18"/>
-      <c r="BD9" s="19" t="s">
+      <c r="AP9" s="15"/>
+      <c r="AQ9" s="15"/>
+      <c r="AR9" s="15"/>
+      <c r="AS9" s="15"/>
+      <c r="AT9" s="15"/>
+      <c r="AU9" s="15"/>
+      <c r="AV9" s="15"/>
+      <c r="AW9" s="15"/>
+      <c r="AX9" s="15"/>
+      <c r="AY9" s="15"/>
+      <c r="AZ9" s="15"/>
+      <c r="BA9" s="15"/>
+      <c r="BB9" s="15"/>
+      <c r="BC9" s="15"/>
+      <c r="BD9" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="BE9" s="18" t="s">
+      <c r="BE9" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="BF9" s="19" t="s">
+      <c r="BF9" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG9" s="18" t="s">
+      <c r="BG9" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="BH9" s="18" t="s">
+      <c r="BH9" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="BI9" s="19" t="s">
+      <c r="BI9" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="BJ9" s="18" t="s">
+      <c r="BJ9" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="BK9" s="18" t="s">
+      <c r="BK9" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="BL9" s="18" t="s">
+      <c r="BL9" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="BM9" s="18" t="s">
+      <c r="BM9" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="BN9" s="21" t="s">
+      <c r="BN9" s="18" t="s">
         <v>1524</v>
       </c>
-      <c r="BO9" s="20">
+      <c r="BO9" s="17">
         <v>30000</v>
       </c>
-      <c r="BP9" s="17" t="s">
+      <c r="BP9" s="14" t="s">
         <v>1535</v>
       </c>
-      <c r="BQ9" s="18"/>
-      <c r="BR9" s="8" t="s">
-        <v>1595</v>
+      <c r="BQ9" s="15"/>
+      <c r="BR9" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="10" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>334</v>
       </c>
@@ -9790,17 +9788,17 @@
       <c r="BN10" t="s">
         <v>1517</v>
       </c>
-      <c r="BO10" s="6">
+      <c r="BO10" s="5">
         <v>200000</v>
       </c>
-      <c r="BP10" s="8" t="s">
+      <c r="BP10" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR10" s="8" t="s">
-        <v>1586</v>
+      <c r="BR10" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="11" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>334</v>
       </c>
@@ -9951,17 +9949,17 @@
       <c r="BN11" t="s">
         <v>1517</v>
       </c>
-      <c r="BO11" s="6">
+      <c r="BO11" s="5">
         <v>200000</v>
       </c>
-      <c r="BP11" s="8" t="s">
+      <c r="BP11" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR11" s="8" t="s">
-        <v>1595</v>
+      <c r="BR11" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="12" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>367</v>
       </c>
@@ -10109,20 +10107,20 @@
       <c r="BK12" t="s">
         <v>686</v>
       </c>
-      <c r="BN12" s="8" t="s">
-        <v>1557</v>
-      </c>
-      <c r="BO12" s="6">
+      <c r="BN12" s="25" t="s">
+        <v>1608</v>
+      </c>
+      <c r="BO12" s="5">
         <v>100000</v>
       </c>
-      <c r="BP12" s="8" t="s">
+      <c r="BP12" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR12" s="8" t="s">
-        <v>1582</v>
+      <c r="BR12" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="13" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>403</v>
       </c>
@@ -10270,101 +10268,101 @@
       <c r="BN13" t="s">
         <v>1517</v>
       </c>
-      <c r="BO13" s="6">
+      <c r="BO13" s="5">
         <v>75000</v>
       </c>
-      <c r="BP13" s="8" t="s">
+      <c r="BP13" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BR13" s="8" t="s">
-        <v>1580</v>
+      <c r="BR13" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="14" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="18" t="s">
+    <row r="14" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="15" t="s">
         <v>1539</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="18"/>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="18"/>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="18"/>
-      <c r="AB14" s="18"/>
-      <c r="AC14" s="18"/>
-      <c r="AD14" s="21" t="s">
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="18" t="s">
         <v>1540</v>
       </c>
-      <c r="AE14" s="18"/>
-      <c r="AF14" s="18" t="s">
+      <c r="AE14" s="15"/>
+      <c r="AF14" s="15" t="s">
         <v>1536</v>
       </c>
-      <c r="AG14" s="18"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="18"/>
-      <c r="AJ14" s="18"/>
-      <c r="AK14" s="18"/>
-      <c r="AL14" s="18"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="18"/>
-      <c r="AO14" s="18"/>
-      <c r="AP14" s="18"/>
-      <c r="AQ14" s="18"/>
-      <c r="AR14" s="18"/>
-      <c r="AS14" s="18"/>
-      <c r="AT14" s="18"/>
-      <c r="AU14" s="18"/>
-      <c r="AV14" s="18"/>
-      <c r="AW14" s="18"/>
-      <c r="AX14" s="18"/>
-      <c r="AY14" s="18"/>
-      <c r="AZ14" s="18"/>
-      <c r="BA14" s="18"/>
-      <c r="BB14" s="18"/>
-      <c r="BC14" s="18"/>
-      <c r="BD14" s="18"/>
-      <c r="BE14" s="18"/>
-      <c r="BF14" s="18"/>
-      <c r="BG14" s="18"/>
-      <c r="BH14" s="18"/>
-      <c r="BI14" s="18"/>
-      <c r="BJ14" s="18"/>
-      <c r="BK14" s="18"/>
-      <c r="BL14" s="18"/>
-      <c r="BM14" s="18"/>
-      <c r="BN14" s="18" t="s">
+      <c r="AG14" s="15"/>
+      <c r="AH14" s="15"/>
+      <c r="AI14" s="15"/>
+      <c r="AJ14" s="15"/>
+      <c r="AK14" s="15"/>
+      <c r="AL14" s="15"/>
+      <c r="AM14" s="15"/>
+      <c r="AN14" s="15"/>
+      <c r="AO14" s="15"/>
+      <c r="AP14" s="15"/>
+      <c r="AQ14" s="15"/>
+      <c r="AR14" s="15"/>
+      <c r="AS14" s="15"/>
+      <c r="AT14" s="15"/>
+      <c r="AU14" s="15"/>
+      <c r="AV14" s="15"/>
+      <c r="AW14" s="15"/>
+      <c r="AX14" s="15"/>
+      <c r="AY14" s="15"/>
+      <c r="AZ14" s="15"/>
+      <c r="BA14" s="15"/>
+      <c r="BB14" s="15"/>
+      <c r="BC14" s="15"/>
+      <c r="BD14" s="15"/>
+      <c r="BE14" s="15"/>
+      <c r="BF14" s="15"/>
+      <c r="BG14" s="15"/>
+      <c r="BH14" s="15"/>
+      <c r="BI14" s="15"/>
+      <c r="BJ14" s="15"/>
+      <c r="BK14" s="15"/>
+      <c r="BL14" s="15"/>
+      <c r="BM14" s="15"/>
+      <c r="BN14" s="15" t="s">
         <v>1517</v>
       </c>
-      <c r="BO14" s="20">
+      <c r="BO14" s="17">
         <v>150000</v>
       </c>
-      <c r="BP14" s="17" t="s">
+      <c r="BP14" s="14" t="s">
         <v>537</v>
       </c>
-      <c r="BQ14" s="18"/>
-      <c r="BR14" s="8" t="s">
-        <v>1595</v>
+      <c r="BQ14" s="15"/>
+      <c r="BR14" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="15" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>440</v>
       </c>
@@ -10383,17 +10381,17 @@
       <c r="BN15" t="s">
         <v>1517</v>
       </c>
-      <c r="BO15" s="6">
+      <c r="BO15" s="5">
         <v>300000</v>
       </c>
-      <c r="BP15" s="8" t="s">
+      <c r="BP15" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR15" s="8" t="s">
-        <v>1585</v>
+      <c r="BR15" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="16" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>440</v>
       </c>
@@ -10550,17 +10548,17 @@
       <c r="BN16" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="BO16" s="6">
+      <c r="BO16" s="5">
         <v>100000</v>
       </c>
-      <c r="BP16" s="5" t="s">
+      <c r="BP16" s="3" t="s">
         <v>1537</v>
       </c>
-      <c r="BR16" s="8" t="s">
-        <v>1585</v>
+      <c r="BR16" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="17" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>440</v>
       </c>
@@ -10711,17 +10709,17 @@
       <c r="BN17" t="s">
         <v>1517</v>
       </c>
-      <c r="BO17" s="6">
+      <c r="BO17" s="5">
         <v>750000</v>
       </c>
-      <c r="BP17" s="8" t="s">
+      <c r="BP17" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="BR17" s="8" t="s">
-        <v>1586</v>
+      <c r="BR17" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="18" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>440</v>
       </c>
@@ -10872,17 +10870,17 @@
       <c r="BN18" t="s">
         <v>1517</v>
       </c>
-      <c r="BO18" s="6">
+      <c r="BO18" s="5">
         <v>500000</v>
       </c>
-      <c r="BP18" s="8" t="s">
+      <c r="BP18" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="BR18" s="8" t="s">
-        <v>1595</v>
+      <c r="BR18" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="19" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>440</v>
       </c>
@@ -11036,17 +11034,17 @@
       <c r="BN19" t="s">
         <v>1517</v>
       </c>
-      <c r="BO19" s="6">
+      <c r="BO19" s="5">
         <v>25000</v>
       </c>
-      <c r="BP19" s="8" t="s">
+      <c r="BP19" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BR19" s="8" t="s">
-        <v>1586</v>
+      <c r="BR19" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="20" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>440</v>
       </c>
@@ -11200,17 +11198,17 @@
       <c r="BN20" t="s">
         <v>1517</v>
       </c>
-      <c r="BO20" s="6">
+      <c r="BO20" s="5">
         <v>25000</v>
       </c>
-      <c r="BP20" s="8" t="s">
+      <c r="BP20" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BR20" s="8" t="s">
-        <v>1595</v>
+      <c r="BR20" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="21" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>440</v>
       </c>
@@ -11370,20 +11368,20 @@
       <c r="BM21" t="s">
         <v>1175</v>
       </c>
-      <c r="BN21" s="8" t="s">
-        <v>1564</v>
-      </c>
-      <c r="BO21" s="6">
+      <c r="BN21" s="7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="BO21" s="5">
         <v>150000</v>
       </c>
-      <c r="BP21" s="8" t="s">
+      <c r="BP21" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR21" s="8" t="s">
-        <v>1586</v>
+      <c r="BR21" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="22" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>440</v>
       </c>
@@ -11543,20 +11541,20 @@
       <c r="BM22" t="s">
         <v>1175</v>
       </c>
-      <c r="BN22" s="8" t="s">
-        <v>1564</v>
-      </c>
-      <c r="BO22" s="6">
+      <c r="BN22" s="7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="BO22" s="5">
         <v>150000</v>
       </c>
-      <c r="BP22" s="8" t="s">
+      <c r="BP22" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR22" s="8" t="s">
-        <v>1595</v>
+      <c r="BR22" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="23" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>440</v>
       </c>
@@ -11704,19 +11702,19 @@
       <c r="BN23" t="s">
         <v>291</v>
       </c>
-      <c r="BO23" s="6">
+      <c r="BO23" s="5">
         <v>125000</v>
       </c>
-      <c r="BP23" s="8" t="s">
+      <c r="BP23" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR23" s="8" t="s">
-        <v>1580</v>
+      <c r="BR23" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="24" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="8" t="s">
-        <v>1558</v>
+    <row r="24" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="7" t="s">
+        <v>1557</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="AD24" s="3" t="s">
@@ -11736,29 +11734,29 @@
       <c r="BG24" s="2"/>
       <c r="BI24" s="2"/>
       <c r="BJ24" s="2"/>
-      <c r="BN24" s="8" t="s">
+      <c r="BN24" s="7" t="s">
         <v>1517</v>
       </c>
-      <c r="BO24" s="6">
+      <c r="BO24" s="5">
         <v>150000</v>
       </c>
-      <c r="BP24" s="8" t="s">
+      <c r="BP24" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BQ24" s="8" t="s">
+      <c r="BQ24" s="7" t="s">
         <v>1541</v>
       </c>
-      <c r="BR24" s="8" t="s">
-        <v>1582</v>
+      <c r="BR24" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="25" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="8" t="s">
-        <v>1575</v>
+    <row r="25" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="7" t="s">
+        <v>1574</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="AD25" s="3"/>
-      <c r="AF25" s="8" t="s">
+      <c r="AF25" s="7" t="s">
         <v>150</v>
       </c>
       <c r="AG25" s="2"/>
@@ -11775,397 +11773,397 @@
       <c r="BG25" s="2"/>
       <c r="BI25" s="2"/>
       <c r="BJ25" s="2"/>
-      <c r="BN25" s="8" t="s">
-        <v>1576</v>
-      </c>
-      <c r="BO25" s="6">
+      <c r="BN25" s="7" t="s">
+        <v>1575</v>
+      </c>
+      <c r="BO25" s="5">
         <v>50000</v>
       </c>
-      <c r="BP25" s="8" t="s">
+      <c r="BP25" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BQ25" s="8"/>
-      <c r="BR25" s="8" t="s">
-        <v>1582</v>
+      <c r="BQ25" s="7"/>
+      <c r="BR25" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="26" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>621</v>
       </c>
       <c r="B26" t="s">
         <v>622</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="15" t="s">
         <v>1212</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="15" t="s">
         <v>1213</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="15" t="s">
         <v>1214</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="15" t="s">
         <v>1175</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="H26" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I26" s="18" t="s">
+      <c r="I26" s="15" t="s">
         <v>1215</v>
       </c>
-      <c r="J26" s="18" t="s">
+      <c r="J26" s="15" t="s">
         <v>1216</v>
       </c>
-      <c r="K26" s="18" t="s">
+      <c r="K26" s="15" t="s">
         <v>1217</v>
       </c>
-      <c r="L26" s="18" t="s">
+      <c r="L26" s="15" t="s">
         <v>1218</v>
       </c>
-      <c r="M26" s="18" t="s">
+      <c r="M26" s="15" t="s">
         <v>1219</v>
       </c>
-      <c r="N26" s="18" t="s">
+      <c r="N26" s="15" t="s">
         <v>1211</v>
       </c>
-      <c r="O26" s="18" t="s">
+      <c r="O26" s="15" t="s">
         <v>1220</v>
       </c>
-      <c r="P26" s="18" t="s">
+      <c r="P26" s="15" t="s">
         <v>1221</v>
       </c>
-      <c r="Q26" s="18" t="s">
+      <c r="Q26" s="15" t="s">
         <v>1222</v>
       </c>
-      <c r="R26" s="18" t="s">
+      <c r="R26" s="15" t="s">
         <v>1223</v>
       </c>
-      <c r="S26" s="18" t="s">
+      <c r="S26" s="15" t="s">
         <v>1224</v>
       </c>
-      <c r="T26" s="18" t="s">
+      <c r="T26" s="15" t="s">
         <v>1225</v>
       </c>
-      <c r="U26" s="18" t="s">
+      <c r="U26" s="15" t="s">
         <v>1226</v>
       </c>
-      <c r="V26" s="18" t="s">
+      <c r="V26" s="15" t="s">
         <v>1227</v>
       </c>
-      <c r="W26" s="18" t="s">
+      <c r="W26" s="15" t="s">
         <v>1228</v>
       </c>
-      <c r="X26" s="18" t="s">
+      <c r="X26" s="15" t="s">
         <v>1228</v>
       </c>
-      <c r="Y26" s="19" t="s">
+      <c r="Y26" s="16" t="s">
         <v>1229</v>
       </c>
-      <c r="Z26" s="19" t="s">
+      <c r="Z26" s="16" t="s">
         <v>1230</v>
       </c>
-      <c r="AA26" s="18" t="s">
+      <c r="AA26" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="AB26" s="18" t="s">
+      <c r="AB26" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="AC26" s="18" t="s">
+      <c r="AC26" s="15" t="s">
         <v>1231</v>
       </c>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18" t="s">
+      <c r="AD26" s="15"/>
+      <c r="AE26" s="15" t="s">
         <v>1232</v>
       </c>
-      <c r="AF26" s="18" t="s">
+      <c r="AF26" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="AG26" s="19" t="s">
+      <c r="AG26" s="16" t="s">
         <v>1233</v>
       </c>
-      <c r="AH26" s="19" t="s">
+      <c r="AH26" s="16" t="s">
         <v>1234</v>
       </c>
-      <c r="AI26" s="19" t="s">
+      <c r="AI26" s="16" t="s">
         <v>1235</v>
       </c>
-      <c r="AJ26" s="18" t="s">
+      <c r="AJ26" s="15" t="s">
         <v>1236</v>
       </c>
-      <c r="AK26" s="19" t="s">
+      <c r="AK26" s="16" t="s">
         <v>1237</v>
       </c>
-      <c r="AL26" s="19" t="s">
+      <c r="AL26" s="16" t="s">
         <v>1238</v>
       </c>
-      <c r="AM26" s="19" t="s">
+      <c r="AM26" s="16" t="s">
         <v>1239</v>
       </c>
-      <c r="AN26" s="19" t="s">
+      <c r="AN26" s="16" t="s">
         <v>1240</v>
       </c>
-      <c r="AO26" s="19" t="s">
+      <c r="AO26" s="16" t="s">
         <v>1241</v>
       </c>
-      <c r="AP26" s="18" t="s">
+      <c r="AP26" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AQ26" s="18" t="s">
+      <c r="AQ26" s="15" t="s">
         <v>1242</v>
       </c>
-      <c r="AR26" s="18" t="s">
+      <c r="AR26" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AS26" s="18" t="s">
+      <c r="AS26" s="15" t="s">
         <v>1242</v>
       </c>
-      <c r="AT26" s="18" t="s">
+      <c r="AT26" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AU26" s="18" t="s">
+      <c r="AU26" s="15" t="s">
         <v>1242</v>
       </c>
-      <c r="AV26" s="18"/>
-      <c r="AW26" s="18"/>
-      <c r="AX26" s="18"/>
-      <c r="AY26" s="18"/>
-      <c r="AZ26" s="18"/>
-      <c r="BA26" s="18"/>
-      <c r="BB26" s="18"/>
-      <c r="BC26" s="18"/>
-      <c r="BD26" s="19" t="s">
+      <c r="AV26" s="15"/>
+      <c r="AW26" s="15"/>
+      <c r="AX26" s="15"/>
+      <c r="AY26" s="15"/>
+      <c r="AZ26" s="15"/>
+      <c r="BA26" s="15"/>
+      <c r="BB26" s="15"/>
+      <c r="BC26" s="15"/>
+      <c r="BD26" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="BE26" s="18" t="s">
+      <c r="BE26" s="15" t="s">
         <v>1243</v>
       </c>
-      <c r="BF26" s="19" t="s">
+      <c r="BF26" s="16" t="s">
         <v>1244</v>
       </c>
-      <c r="BG26" s="19" t="s">
+      <c r="BG26" s="16" t="s">
         <v>1207</v>
       </c>
-      <c r="BH26" s="18" t="s">
+      <c r="BH26" s="15" t="s">
         <v>1245</v>
       </c>
-      <c r="BI26" s="19" t="s">
+      <c r="BI26" s="16" t="s">
         <v>1246</v>
       </c>
-      <c r="BJ26" s="18" t="s">
+      <c r="BJ26" s="15" t="s">
         <v>1247</v>
       </c>
-      <c r="BK26" s="18"/>
-      <c r="BL26" s="18"/>
-      <c r="BM26" s="18" t="s">
+      <c r="BK26" s="15"/>
+      <c r="BL26" s="15"/>
+      <c r="BM26" s="15" t="s">
         <v>1215</v>
       </c>
-      <c r="BN26" s="18" t="s">
+      <c r="BN26" s="15" t="s">
         <v>1175</v>
       </c>
-      <c r="BO26" s="20">
+      <c r="BO26" s="17">
         <v>310500</v>
       </c>
-      <c r="BP26" s="17" t="s">
+      <c r="BP26" s="14" t="s">
         <v>1530</v>
       </c>
-      <c r="BQ26" s="18"/>
-      <c r="BR26" s="17" t="s">
-        <v>1586</v>
+      <c r="BQ26" s="15"/>
+      <c r="BR26" s="14" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="27" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>621</v>
       </c>
       <c r="B27" t="s">
         <v>622</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="15" t="s">
         <v>1212</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="15" t="s">
         <v>1213</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="15" t="s">
         <v>1214</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="15" t="s">
         <v>1175</v>
       </c>
-      <c r="H27" s="18" t="s">
+      <c r="H27" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="15" t="s">
         <v>1215</v>
       </c>
-      <c r="J27" s="18" t="s">
+      <c r="J27" s="15" t="s">
         <v>1216</v>
       </c>
-      <c r="K27" s="18" t="s">
+      <c r="K27" s="15" t="s">
         <v>1217</v>
       </c>
-      <c r="L27" s="18" t="s">
+      <c r="L27" s="15" t="s">
         <v>1218</v>
       </c>
-      <c r="M27" s="18" t="s">
+      <c r="M27" s="15" t="s">
         <v>1219</v>
       </c>
-      <c r="N27" s="18" t="s">
+      <c r="N27" s="15" t="s">
         <v>1211</v>
       </c>
-      <c r="O27" s="18" t="s">
+      <c r="O27" s="15" t="s">
         <v>1220</v>
       </c>
-      <c r="P27" s="18" t="s">
+      <c r="P27" s="15" t="s">
         <v>1221</v>
       </c>
-      <c r="Q27" s="18" t="s">
+      <c r="Q27" s="15" t="s">
         <v>1222</v>
       </c>
-      <c r="R27" s="18" t="s">
+      <c r="R27" s="15" t="s">
         <v>1223</v>
       </c>
-      <c r="S27" s="18" t="s">
+      <c r="S27" s="15" t="s">
         <v>1224</v>
       </c>
-      <c r="T27" s="18" t="s">
+      <c r="T27" s="15" t="s">
         <v>1225</v>
       </c>
-      <c r="U27" s="18" t="s">
+      <c r="U27" s="15" t="s">
         <v>1226</v>
       </c>
-      <c r="V27" s="18" t="s">
+      <c r="V27" s="15" t="s">
         <v>1227</v>
       </c>
-      <c r="W27" s="18" t="s">
+      <c r="W27" s="15" t="s">
         <v>1228</v>
       </c>
-      <c r="X27" s="18" t="s">
+      <c r="X27" s="15" t="s">
         <v>1228</v>
       </c>
-      <c r="Y27" s="19" t="s">
+      <c r="Y27" s="16" t="s">
         <v>1229</v>
       </c>
-      <c r="Z27" s="19" t="s">
+      <c r="Z27" s="16" t="s">
         <v>1230</v>
       </c>
-      <c r="AA27" s="18" t="s">
+      <c r="AA27" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="AB27" s="18" t="s">
+      <c r="AB27" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="AC27" s="18" t="s">
+      <c r="AC27" s="15" t="s">
         <v>1231</v>
       </c>
-      <c r="AD27" s="18"/>
-      <c r="AE27" s="18" t="s">
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15" t="s">
         <v>1232</v>
       </c>
-      <c r="AF27" s="18" t="s">
+      <c r="AF27" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="AG27" s="19" t="s">
+      <c r="AG27" s="16" t="s">
         <v>1233</v>
       </c>
-      <c r="AH27" s="19" t="s">
+      <c r="AH27" s="16" t="s">
         <v>1234</v>
       </c>
-      <c r="AI27" s="19" t="s">
+      <c r="AI27" s="16" t="s">
         <v>1235</v>
       </c>
-      <c r="AJ27" s="18" t="s">
+      <c r="AJ27" s="15" t="s">
         <v>1236</v>
       </c>
-      <c r="AK27" s="19" t="s">
+      <c r="AK27" s="16" t="s">
         <v>1237</v>
       </c>
-      <c r="AL27" s="19" t="s">
+      <c r="AL27" s="16" t="s">
         <v>1238</v>
       </c>
-      <c r="AM27" s="19" t="s">
+      <c r="AM27" s="16" t="s">
         <v>1239</v>
       </c>
-      <c r="AN27" s="19" t="s">
+      <c r="AN27" s="16" t="s">
         <v>1240</v>
       </c>
-      <c r="AO27" s="19" t="s">
+      <c r="AO27" s="16" t="s">
         <v>1241</v>
       </c>
-      <c r="AP27" s="18" t="s">
+      <c r="AP27" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AQ27" s="18" t="s">
+      <c r="AQ27" s="15" t="s">
         <v>1242</v>
       </c>
-      <c r="AR27" s="18" t="s">
+      <c r="AR27" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AS27" s="18" t="s">
+      <c r="AS27" s="15" t="s">
         <v>1242</v>
       </c>
-      <c r="AT27" s="18" t="s">
+      <c r="AT27" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AU27" s="18" t="s">
+      <c r="AU27" s="15" t="s">
         <v>1242</v>
       </c>
-      <c r="AV27" s="18"/>
-      <c r="AW27" s="18"/>
-      <c r="AX27" s="18"/>
-      <c r="AY27" s="18"/>
-      <c r="AZ27" s="18"/>
-      <c r="BA27" s="18"/>
-      <c r="BB27" s="18"/>
-      <c r="BC27" s="18"/>
-      <c r="BD27" s="19" t="s">
+      <c r="AV27" s="15"/>
+      <c r="AW27" s="15"/>
+      <c r="AX27" s="15"/>
+      <c r="AY27" s="15"/>
+      <c r="AZ27" s="15"/>
+      <c r="BA27" s="15"/>
+      <c r="BB27" s="15"/>
+      <c r="BC27" s="15"/>
+      <c r="BD27" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="BE27" s="18" t="s">
+      <c r="BE27" s="15" t="s">
         <v>1243</v>
       </c>
-      <c r="BF27" s="19" t="s">
+      <c r="BF27" s="16" t="s">
         <v>1244</v>
       </c>
-      <c r="BG27" s="19" t="s">
+      <c r="BG27" s="16" t="s">
         <v>1207</v>
       </c>
-      <c r="BH27" s="18" t="s">
+      <c r="BH27" s="15" t="s">
         <v>1245</v>
       </c>
-      <c r="BI27" s="19" t="s">
+      <c r="BI27" s="16" t="s">
         <v>1246</v>
       </c>
-      <c r="BJ27" s="18" t="s">
+      <c r="BJ27" s="15" t="s">
         <v>1247</v>
       </c>
-      <c r="BK27" s="18"/>
-      <c r="BL27" s="18"/>
-      <c r="BM27" s="18" t="s">
+      <c r="BK27" s="15"/>
+      <c r="BL27" s="15"/>
+      <c r="BM27" s="15" t="s">
         <v>1215</v>
       </c>
-      <c r="BN27" s="18" t="s">
+      <c r="BN27" s="15" t="s">
         <v>1175</v>
       </c>
-      <c r="BO27" s="20">
+      <c r="BO27" s="17">
         <v>560499</v>
       </c>
-      <c r="BP27" s="17" t="s">
+      <c r="BP27" s="14" t="s">
         <v>1530</v>
       </c>
-      <c r="BQ27" s="18"/>
-      <c r="BR27" s="17" t="s">
-        <v>1595</v>
+      <c r="BQ27" s="15"/>
+      <c r="BR27" s="14" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="28" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>621</v>
       </c>
@@ -12322,20 +12320,20 @@
       <c r="BJ28" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="BN28" s="8" t="s">
+      <c r="BN28" s="7" t="s">
         <v>1550</v>
       </c>
-      <c r="BO28" s="6">
+      <c r="BO28" s="5">
         <v>200000</v>
       </c>
-      <c r="BP28" s="8" t="s">
+      <c r="BP28" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR28" s="8" t="s">
-        <v>1580</v>
+      <c r="BR28" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="29" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>687</v>
       </c>
@@ -12522,17 +12520,17 @@
       <c r="BN29" t="s">
         <v>1526</v>
       </c>
-      <c r="BO29" s="6">
+      <c r="BO29" s="5">
         <v>100000</v>
       </c>
-      <c r="BP29" s="8" t="s">
+      <c r="BP29" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR29" s="8" t="s">
-        <v>1582</v>
+      <c r="BR29" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="30" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>687</v>
       </c>
@@ -12680,17 +12678,17 @@
       <c r="BN30" t="s">
         <v>1517</v>
       </c>
-      <c r="BO30" s="6">
+      <c r="BO30" s="5">
         <v>125000</v>
       </c>
-      <c r="BP30" s="8" t="s">
+      <c r="BP30" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR30" s="8" t="s">
-        <v>1580</v>
+      <c r="BR30" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="31" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>754</v>
       </c>
@@ -12838,17 +12836,17 @@
       <c r="BN31" t="s">
         <v>969</v>
       </c>
-      <c r="BO31" s="14">
+      <c r="BO31" s="13">
         <v>150000</v>
       </c>
       <c r="BP31" t="s">
         <v>1535</v>
       </c>
-      <c r="BR31" s="8" t="s">
-        <v>1580</v>
+      <c r="BR31" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="32" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>789</v>
       </c>
@@ -12864,43 +12862,43 @@
       <c r="BN32" t="s">
         <v>1517</v>
       </c>
-      <c r="BO32" s="6">
+      <c r="BO32" s="5">
         <v>2100000</v>
       </c>
       <c r="BP32" t="s">
         <v>1530</v>
       </c>
-      <c r="BR32" s="8" t="s">
-        <v>1585</v>
+      <c r="BR32" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="33" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="8" t="s">
-        <v>1559</v>
-      </c>
-      <c r="AD33" s="11" t="s">
+    <row r="33" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" s="7" t="s">
+        <v>1558</v>
+      </c>
+      <c r="AD33" s="10" t="s">
         <v>1556</v>
       </c>
-      <c r="AF33" s="8" t="s">
+      <c r="AF33" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BN33" s="12" t="s">
+      <c r="BN33" s="11" t="s">
         <v>1517</v>
       </c>
-      <c r="BO33" s="6">
+      <c r="BO33" s="5">
         <v>150000</v>
       </c>
-      <c r="BP33" s="8" t="s">
+      <c r="BP33" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="BQ33" s="8" t="s">
+      <c r="BQ33" s="7" t="s">
         <v>1541</v>
       </c>
-      <c r="BR33" s="8" t="s">
-        <v>1582</v>
+      <c r="BR33" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="34" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>900</v>
       </c>
@@ -13033,17 +13031,17 @@
       <c r="BN34" t="s">
         <v>1517</v>
       </c>
-      <c r="BO34" s="6">
+      <c r="BO34" s="5">
         <v>150000</v>
       </c>
-      <c r="BP34" s="8" t="s">
+      <c r="BP34" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR34" s="8" t="s">
-        <v>1586</v>
+      <c r="BR34" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="35" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>900</v>
       </c>
@@ -13176,25 +13174,25 @@
       <c r="BN35" t="s">
         <v>1517</v>
       </c>
-      <c r="BO35" s="6">
+      <c r="BO35" s="5">
         <v>150000</v>
       </c>
-      <c r="BP35" s="8" t="s">
+      <c r="BP35" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR35" s="8" t="s">
-        <v>1595</v>
+      <c r="BR35" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="36" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="8" t="s">
+    <row r="36" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="7" t="s">
         <v>1548</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="AD36" s="2" t="s">
         <v>1549</v>
       </c>
-      <c r="AF36" s="8" t="s">
+      <c r="AF36" s="7" t="s">
         <v>352</v>
       </c>
       <c r="AG36" s="2"/>
@@ -13208,20 +13206,20 @@
       <c r="BF36" s="2"/>
       <c r="BG36" s="2"/>
       <c r="BI36" s="2"/>
-      <c r="BN36" s="8" t="s">
+      <c r="BN36" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="BO36" s="6">
+      <c r="BO36" s="5">
         <v>100000</v>
       </c>
-      <c r="BP36" s="8" t="s">
+      <c r="BP36" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR36" s="8" t="s">
-        <v>1580</v>
+      <c r="BR36" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="37" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>934</v>
       </c>
@@ -13390,17 +13388,17 @@
       <c r="BN37" s="3" t="s">
         <v>1525</v>
       </c>
-      <c r="BO37" s="6">
+      <c r="BO37" s="5">
         <v>150000</v>
       </c>
       <c r="BP37" t="s">
         <v>102</v>
       </c>
-      <c r="BR37" s="8" t="s">
-        <v>1585</v>
+      <c r="BR37" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="38" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>934</v>
       </c>
@@ -13494,7 +13492,7 @@
       <c r="AE38" t="s">
         <v>1336</v>
       </c>
-      <c r="AF38" s="8" t="s">
+      <c r="AF38" s="7" t="s">
         <v>1547</v>
       </c>
       <c r="AG38" s="2" t="s">
@@ -13551,17 +13549,17 @@
       <c r="BN38" t="s">
         <v>1352</v>
       </c>
-      <c r="BO38" s="6">
+      <c r="BO38" s="5">
         <v>1000000</v>
       </c>
-      <c r="BP38" s="8" t="s">
+      <c r="BP38" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="BR38" s="8" t="s">
-        <v>1595</v>
+      <c r="BR38" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="39" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>934</v>
       </c>
@@ -13655,7 +13653,7 @@
       <c r="AE39" t="s">
         <v>1336</v>
       </c>
-      <c r="AF39" s="8" t="s">
+      <c r="AF39" s="7" t="s">
         <v>1547</v>
       </c>
       <c r="AG39" s="2" t="s">
@@ -13712,17 +13710,17 @@
       <c r="BN39" t="s">
         <v>1352</v>
       </c>
-      <c r="BO39" s="6">
+      <c r="BO39" s="5">
         <v>1500000</v>
       </c>
-      <c r="BP39" s="8" t="s">
+      <c r="BP39" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="BR39" s="8" t="s">
-        <v>1586</v>
+      <c r="BR39" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="40" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>934</v>
       </c>
@@ -13876,20 +13874,20 @@
       <c r="BM40" t="s">
         <v>402</v>
       </c>
-      <c r="BN40" s="8" t="s">
-        <v>1560</v>
-      </c>
-      <c r="BO40" s="6">
+      <c r="BN40" s="7" t="s">
+        <v>1559</v>
+      </c>
+      <c r="BO40" s="5">
         <v>50000</v>
       </c>
-      <c r="BP40" s="8" t="s">
+      <c r="BP40" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR40" s="8" t="s">
-        <v>1582</v>
+      <c r="BR40" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="41" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>934</v>
       </c>
@@ -14040,17 +14038,17 @@
       <c r="BN41" t="s">
         <v>865</v>
       </c>
-      <c r="BO41" s="6">
+      <c r="BO41" s="5">
         <v>175000</v>
       </c>
-      <c r="BP41" s="8" t="s">
+      <c r="BP41" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR41" s="8" t="s">
-        <v>1586</v>
+      <c r="BR41" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="42" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>934</v>
       </c>
@@ -14201,17 +14199,17 @@
       <c r="BN42" t="s">
         <v>865</v>
       </c>
-      <c r="BO42" s="6">
+      <c r="BO42" s="5">
         <v>300000</v>
       </c>
-      <c r="BP42" s="8" t="s">
-        <v>1571</v>
-      </c>
-      <c r="BR42" s="8" t="s">
-        <v>1586</v>
+      <c r="BP42" s="7" t="s">
+        <v>1570</v>
+      </c>
+      <c r="BR42" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="43" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>934</v>
       </c>
@@ -14362,20 +14360,20 @@
       <c r="BN43" t="s">
         <v>865</v>
       </c>
-      <c r="BO43" s="6">
+      <c r="BO43" s="5">
         <v>25000</v>
       </c>
-      <c r="BP43" s="8" t="s">
+      <c r="BP43" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BQ43" s="8" t="s">
-        <v>1573</v>
-      </c>
-      <c r="BR43" s="8" t="s">
-        <v>1595</v>
+      <c r="BQ43" s="7" t="s">
+        <v>1572</v>
+      </c>
+      <c r="BR43" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="44" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>934</v>
       </c>
@@ -14526,20 +14524,20 @@
       <c r="BN44" t="s">
         <v>865</v>
       </c>
-      <c r="BO44" s="6">
+      <c r="BO44" s="5">
         <v>25000</v>
       </c>
-      <c r="BP44" s="8" t="s">
+      <c r="BP44" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BQ44" s="8" t="s">
-        <v>1573</v>
-      </c>
-      <c r="BR44" s="8" t="s">
-        <v>1580</v>
+      <c r="BQ44" s="7" t="s">
+        <v>1572</v>
+      </c>
+      <c r="BR44" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="45" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>1072</v>
       </c>
@@ -14735,19 +14733,19 @@
       <c r="BN45" t="s">
         <v>1513</v>
       </c>
-      <c r="BO45" s="6">
+      <c r="BO45" s="5">
         <v>150000</v>
       </c>
-      <c r="BP45" s="8" t="s">
+      <c r="BP45" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR45" s="8" t="s">
-        <v>1582</v>
+      <c r="BR45" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="46" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C46" s="8" t="s">
-        <v>1565</v>
+    <row r="46" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="7" t="s">
+        <v>1564</v>
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
@@ -14766,22 +14764,22 @@
       <c r="BG46" s="2"/>
       <c r="BI46" s="2"/>
       <c r="BJ46" s="2"/>
-      <c r="BN46" s="8" t="s">
+      <c r="BN46" s="7" t="s">
         <v>1003</v>
       </c>
-      <c r="BO46" s="6">
+      <c r="BO46" s="5">
         <v>50000</v>
       </c>
-      <c r="BP46" s="8" t="s">
+      <c r="BP46" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR46" s="8" t="s">
-        <v>1586</v>
+      <c r="BR46" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="47" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C47" s="8" t="s">
-        <v>1565</v>
+    <row r="47" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C47" s="7" t="s">
+        <v>1564</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
@@ -14800,20 +14798,20 @@
       <c r="BG47" s="2"/>
       <c r="BI47" s="2"/>
       <c r="BJ47" s="2"/>
-      <c r="BN47" s="8" t="s">
+      <c r="BN47" s="7" t="s">
         <v>1003</v>
       </c>
-      <c r="BO47" s="6">
+      <c r="BO47" s="5">
         <v>50000</v>
       </c>
-      <c r="BP47" s="8" t="s">
+      <c r="BP47" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR47" s="8" t="s">
-        <v>1595</v>
+      <c r="BR47" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="48" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>1140</v>
       </c>
@@ -14964,17 +14962,17 @@
       <c r="BN48" t="s">
         <v>1387</v>
       </c>
-      <c r="BO48" s="6">
+      <c r="BO48" s="5">
         <v>75000</v>
       </c>
-      <c r="BP48" s="8" t="s">
+      <c r="BP48" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR48" s="8" t="s">
-        <v>1586</v>
+      <c r="BR48" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="49" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>1140</v>
       </c>
@@ -15125,17 +15123,17 @@
       <c r="BN49" t="s">
         <v>1387</v>
       </c>
-      <c r="BO49" s="6">
+      <c r="BO49" s="5">
         <v>200000</v>
       </c>
-      <c r="BP49" s="8" t="s">
+      <c r="BP49" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="BR49" s="8" t="s">
-        <v>1595</v>
+      <c r="BR49" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="50" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>1168</v>
       </c>
@@ -15304,17 +15302,17 @@
       <c r="BN50" t="s">
         <v>173</v>
       </c>
-      <c r="BO50" s="6">
+      <c r="BO50" s="5">
         <v>125000</v>
       </c>
       <c r="BP50" t="s">
         <v>1535</v>
       </c>
-      <c r="BR50" s="8" t="s">
-        <v>1585</v>
+      <c r="BR50" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="51" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>1171</v>
       </c>
@@ -15471,17 +15469,17 @@
       <c r="BN51" t="s">
         <v>620</v>
       </c>
-      <c r="BO51" s="6">
+      <c r="BO51" s="5">
         <v>100000</v>
       </c>
-      <c r="BP51" s="8" t="s">
+      <c r="BP51" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR51" s="8" t="s">
-        <v>1582</v>
+      <c r="BR51" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="52" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>1172</v>
       </c>
@@ -15497,17 +15495,17 @@
       <c r="AF52" t="s">
         <v>1547</v>
       </c>
-      <c r="BO52" s="6">
+      <c r="BO52" s="5">
         <v>500000</v>
       </c>
       <c r="BP52" t="s">
         <v>1533</v>
       </c>
-      <c r="BR52" s="8" t="s">
-        <v>1585</v>
+      <c r="BR52" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="53" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>1176</v>
       </c>
@@ -15652,20 +15650,20 @@
       <c r="BJ53" t="s">
         <v>899</v>
       </c>
-      <c r="BN53" s="8" t="s">
+      <c r="BN53" s="7" t="s">
         <v>1551</v>
       </c>
-      <c r="BO53" s="6">
+      <c r="BO53" s="5">
         <v>200000</v>
       </c>
-      <c r="BP53" s="8" t="s">
+      <c r="BP53" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR53" s="8" t="s">
-        <v>1580</v>
+      <c r="BR53" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="54" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>1176</v>
       </c>
@@ -15810,20 +15808,20 @@
       <c r="BJ54" t="s">
         <v>899</v>
       </c>
-      <c r="BN54" s="8" t="s">
+      <c r="BN54" s="7" t="s">
         <v>1551</v>
       </c>
-      <c r="BO54" s="6">
+      <c r="BO54" s="5">
         <v>50000</v>
       </c>
-      <c r="BP54" s="8" t="s">
-        <v>1566</v>
-      </c>
-      <c r="BR54" s="8" t="s">
-        <v>1586</v>
+      <c r="BP54" s="7" t="s">
+        <v>1565</v>
+      </c>
+      <c r="BR54" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="55" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>1210</v>
       </c>
@@ -15980,17 +15978,17 @@
       <c r="BN55" t="s">
         <v>121</v>
       </c>
-      <c r="BO55" s="6">
+      <c r="BO55" s="5">
         <v>100000</v>
       </c>
-      <c r="BP55" s="8" t="s">
+      <c r="BP55" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR55" s="8" t="s">
-        <v>1582</v>
+      <c r="BR55" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="56" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>1283</v>
       </c>
@@ -16141,17 +16139,17 @@
       <c r="BN56" t="s">
         <v>518</v>
       </c>
-      <c r="BO56" s="6">
+      <c r="BO56" s="5">
         <v>275000</v>
       </c>
-      <c r="BP56" s="8" t="s">
+      <c r="BP56" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR56" s="8" t="s">
-        <v>1586</v>
+      <c r="BR56" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="57" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>1283</v>
       </c>
@@ -16302,17 +16300,17 @@
       <c r="BN57" t="s">
         <v>518</v>
       </c>
-      <c r="BO57" s="6">
+      <c r="BO57" s="5">
         <v>30000</v>
       </c>
-      <c r="BP57" s="8" t="s">
+      <c r="BP57" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR57" s="8" t="s">
-        <v>1586</v>
+      <c r="BR57" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="58" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>1283</v>
       </c>
@@ -16463,17 +16461,17 @@
       <c r="BN58" t="s">
         <v>518</v>
       </c>
-      <c r="BO58" s="6">
+      <c r="BO58" s="5">
         <v>150000</v>
       </c>
-      <c r="BP58" s="8" t="s">
+      <c r="BP58" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR58" s="8" t="s">
-        <v>1595</v>
+      <c r="BR58" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="59" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>1315</v>
       </c>
@@ -16624,17 +16622,17 @@
       <c r="BN59" t="s">
         <v>1517</v>
       </c>
-      <c r="BO59" s="6">
+      <c r="BO59" s="5">
         <v>200000</v>
       </c>
-      <c r="BP59" s="8" t="s">
+      <c r="BP59" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR59" s="8" t="s">
-        <v>1586</v>
+      <c r="BR59" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="60" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>1315</v>
       </c>
@@ -16785,25 +16783,25 @@
       <c r="BN60" t="s">
         <v>1517</v>
       </c>
-      <c r="BO60" s="6">
+      <c r="BO60" s="5">
         <v>200000</v>
       </c>
-      <c r="BP60" s="8" t="s">
+      <c r="BP60" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR60" s="8" t="s">
-        <v>1595</v>
+      <c r="BR60" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="61" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C61" s="8" t="s">
-        <v>1569</v>
+    <row r="61" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="7" t="s">
+        <v>1568</v>
       </c>
       <c r="Z61" s="2"/>
-      <c r="AD61" s="11" t="s">
-        <v>1577</v>
-      </c>
-      <c r="AF61" s="8" t="s">
+      <c r="AD61" s="10" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AF61" s="7" t="s">
         <v>1547</v>
       </c>
       <c r="AG61" s="2"/>
@@ -16820,28 +16818,28 @@
       <c r="BG61" s="2"/>
       <c r="BI61" s="2"/>
       <c r="BJ61" s="2"/>
-      <c r="BN61" s="8" t="s">
-        <v>1578</v>
-      </c>
-      <c r="BO61" s="6">
+      <c r="BN61" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="BO61" s="5">
         <v>250000</v>
       </c>
-      <c r="BP61" s="8" t="s">
+      <c r="BP61" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="BR61" s="8" t="s">
-        <v>1586</v>
+      <c r="BR61" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="62" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C62" s="8" t="s">
-        <v>1569</v>
+    <row r="62" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="7" t="s">
+        <v>1568</v>
       </c>
       <c r="Z62" s="2"/>
-      <c r="AD62" s="11" t="s">
-        <v>1577</v>
-      </c>
-      <c r="AF62" s="8" t="s">
+      <c r="AD62" s="10" t="s">
+        <v>1576</v>
+      </c>
+      <c r="AF62" s="7" t="s">
         <v>1547</v>
       </c>
       <c r="AG62" s="2"/>
@@ -16858,28 +16856,28 @@
       <c r="BG62" s="2"/>
       <c r="BI62" s="2"/>
       <c r="BJ62" s="2"/>
-      <c r="BN62" s="8" t="s">
-        <v>1578</v>
-      </c>
-      <c r="BO62" s="6">
+      <c r="BN62" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="BO62" s="5">
         <v>750000</v>
       </c>
-      <c r="BP62" s="8" t="s">
+      <c r="BP62" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="BR62" s="8" t="s">
-        <v>1595</v>
+      <c r="BR62" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="63" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C63" s="8" t="s">
+    <row r="63" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="7" t="s">
         <v>1552</v>
       </c>
       <c r="Z63" s="2"/>
       <c r="AD63" s="2" t="s">
         <v>1553</v>
       </c>
-      <c r="AF63" s="8" t="s">
+      <c r="AF63" s="7" t="s">
         <v>1536</v>
       </c>
       <c r="AG63" s="2"/>
@@ -16896,23 +16894,23 @@
       <c r="BG63" s="2"/>
       <c r="BI63" s="2"/>
       <c r="BJ63" s="2"/>
-      <c r="BN63" s="8" t="s">
+      <c r="BN63" s="7" t="s">
         <v>1517</v>
       </c>
-      <c r="BO63" s="6">
+      <c r="BO63" s="5">
         <v>200000</v>
       </c>
-      <c r="BP63" s="8" t="s">
+      <c r="BP63" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BQ63" s="8" t="s">
+      <c r="BQ63" s="7" t="s">
         <v>1541</v>
       </c>
-      <c r="BR63" s="8" t="s">
-        <v>1580</v>
+      <c r="BR63" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="64" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>1353</v>
       </c>
@@ -16928,17 +16926,17 @@
       <c r="BN64" t="s">
         <v>1532</v>
       </c>
-      <c r="BO64" s="6">
+      <c r="BO64" s="5">
         <v>350000</v>
       </c>
       <c r="BP64" t="s">
         <v>1533</v>
       </c>
-      <c r="BR64" s="8" t="s">
-        <v>1585</v>
+      <c r="BR64" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="65" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>1388</v>
       </c>
@@ -17089,17 +17087,17 @@
       <c r="BN65" t="s">
         <v>291</v>
       </c>
-      <c r="BO65" s="6">
+      <c r="BO65" s="5">
         <v>150000</v>
       </c>
-      <c r="BP65" s="8" t="s">
+      <c r="BP65" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR65" s="8" t="s">
-        <v>1582</v>
+      <c r="BR65" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="66" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>1422</v>
       </c>
@@ -17254,17 +17252,17 @@
       <c r="BN66" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="BO66" s="6">
+      <c r="BO66" s="5">
         <v>150000</v>
       </c>
-      <c r="BP66" s="5" t="s">
+      <c r="BP66" s="3" t="s">
         <v>1538</v>
       </c>
-      <c r="BR66" s="8" t="s">
-        <v>1585</v>
+      <c r="BR66" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="67" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>1445</v>
       </c>
@@ -17283,17 +17281,17 @@
       <c r="BN67" t="s">
         <v>1532</v>
       </c>
-      <c r="BO67" s="6">
+      <c r="BO67" s="5">
         <v>100000</v>
       </c>
       <c r="BP67" t="s">
         <v>1535</v>
       </c>
-      <c r="BR67" s="8" t="s">
-        <v>1585</v>
+      <c r="BR67" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="68" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>1445</v>
       </c>
@@ -17444,17 +17442,17 @@
       <c r="BN68" t="s">
         <v>121</v>
       </c>
-      <c r="BO68" s="6">
+      <c r="BO68" s="5">
         <v>100000</v>
       </c>
-      <c r="BP68" s="8" t="s">
+      <c r="BP68" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR68" s="8" t="s">
-        <v>1582</v>
+      <c r="BR68" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="69" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>1512</v>
       </c>
@@ -17614,99 +17612,99 @@
       <c r="BN69" t="s">
         <v>291</v>
       </c>
-      <c r="BO69" s="6">
+      <c r="BO69" s="5">
         <v>125000</v>
       </c>
       <c r="BP69" t="s">
         <v>1535</v>
       </c>
-      <c r="BR69" s="8" t="s">
-        <v>1585</v>
+      <c r="BR69" s="7" t="s">
+        <v>1584</v>
       </c>
     </row>
-    <row r="70" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C70" s="17" t="s">
+    <row r="70" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="14" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="15"/>
+      <c r="S70" s="15"/>
+      <c r="T70" s="15"/>
+      <c r="U70" s="15"/>
+      <c r="V70" s="15"/>
+      <c r="W70" s="15"/>
+      <c r="X70" s="15"/>
+      <c r="Y70" s="16"/>
+      <c r="Z70" s="16"/>
+      <c r="AA70" s="15"/>
+      <c r="AB70" s="15"/>
+      <c r="AC70" s="15"/>
+      <c r="AD70" s="16"/>
+      <c r="AE70" s="15"/>
+      <c r="AF70" s="14" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AG70" s="16"/>
+      <c r="AH70" s="16"/>
+      <c r="AI70" s="16"/>
+      <c r="AJ70" s="15"/>
+      <c r="AK70" s="16"/>
+      <c r="AL70" s="16"/>
+      <c r="AM70" s="16"/>
+      <c r="AN70" s="16"/>
+      <c r="AO70" s="16"/>
+      <c r="AP70" s="15"/>
+      <c r="AQ70" s="15"/>
+      <c r="AR70" s="15"/>
+      <c r="AS70" s="15"/>
+      <c r="AT70" s="15"/>
+      <c r="AU70" s="15"/>
+      <c r="AV70" s="15"/>
+      <c r="AW70" s="15"/>
+      <c r="AX70" s="15"/>
+      <c r="AY70" s="15"/>
+      <c r="AZ70" s="15"/>
+      <c r="BA70" s="15"/>
+      <c r="BB70" s="15"/>
+      <c r="BC70" s="15"/>
+      <c r="BD70" s="16"/>
+      <c r="BE70" s="15"/>
+      <c r="BF70" s="15"/>
+      <c r="BG70" s="16"/>
+      <c r="BH70" s="15"/>
+      <c r="BI70" s="16"/>
+      <c r="BJ70" s="15"/>
+      <c r="BK70" s="15"/>
+      <c r="BL70" s="15"/>
+      <c r="BM70" s="15"/>
+      <c r="BN70" s="14" t="s">
         <v>1583</v>
       </c>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="18"/>
-      <c r="P70" s="18"/>
-      <c r="Q70" s="18"/>
-      <c r="R70" s="18"/>
-      <c r="S70" s="18"/>
-      <c r="T70" s="18"/>
-      <c r="U70" s="18"/>
-      <c r="V70" s="18"/>
-      <c r="W70" s="18"/>
-      <c r="X70" s="18"/>
-      <c r="Y70" s="19"/>
-      <c r="Z70" s="19"/>
-      <c r="AA70" s="18"/>
-      <c r="AB70" s="18"/>
-      <c r="AC70" s="18"/>
-      <c r="AD70" s="19"/>
-      <c r="AE70" s="18"/>
-      <c r="AF70" s="17" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AG70" s="19"/>
-      <c r="AH70" s="19"/>
-      <c r="AI70" s="19"/>
-      <c r="AJ70" s="18"/>
-      <c r="AK70" s="19"/>
-      <c r="AL70" s="19"/>
-      <c r="AM70" s="19"/>
-      <c r="AN70" s="19"/>
-      <c r="AO70" s="19"/>
-      <c r="AP70" s="18"/>
-      <c r="AQ70" s="18"/>
-      <c r="AR70" s="18"/>
-      <c r="AS70" s="18"/>
-      <c r="AT70" s="18"/>
-      <c r="AU70" s="18"/>
-      <c r="AV70" s="18"/>
-      <c r="AW70" s="18"/>
-      <c r="AX70" s="18"/>
-      <c r="AY70" s="18"/>
-      <c r="AZ70" s="18"/>
-      <c r="BA70" s="18"/>
-      <c r="BB70" s="18"/>
-      <c r="BC70" s="18"/>
-      <c r="BD70" s="19"/>
-      <c r="BE70" s="18"/>
-      <c r="BF70" s="18"/>
-      <c r="BG70" s="19"/>
-      <c r="BH70" s="18"/>
-      <c r="BI70" s="19"/>
-      <c r="BJ70" s="18"/>
-      <c r="BK70" s="18"/>
-      <c r="BL70" s="18"/>
-      <c r="BM70" s="18"/>
-      <c r="BN70" s="17" t="s">
-        <v>1584</v>
-      </c>
-      <c r="BO70" s="20">
+      <c r="BO70" s="17">
         <v>275000</v>
       </c>
-      <c r="BP70" s="17" t="s">
+      <c r="BP70" s="14" t="s">
         <v>1533</v>
       </c>
-      <c r="BQ70" s="18"/>
-      <c r="BR70" s="17" t="s">
-        <v>1582</v>
+      <c r="BQ70" s="15"/>
+      <c r="BR70" s="14" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="71" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C71" t="s">
         <v>405</v>
       </c>
@@ -17857,17 +17855,17 @@
       <c r="BN71" t="s">
         <v>439</v>
       </c>
-      <c r="BO71" s="6">
+      <c r="BO71" s="5">
         <v>150000</v>
       </c>
-      <c r="BP71" s="8" t="s">
+      <c r="BP71" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BR71" s="8" t="s">
-        <v>1582</v>
+      <c r="BR71" s="7" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="72" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" t="s">
         <v>791</v>
       </c>
@@ -17955,7 +17953,7 @@
       <c r="AE72" t="s">
         <v>810</v>
       </c>
-      <c r="AF72" s="11" t="s">
+      <c r="AF72" s="10" t="s">
         <v>69</v>
       </c>
       <c r="AG72" t="s">
@@ -18027,209 +18025,209 @@
       <c r="BK72" t="s">
         <v>827</v>
       </c>
-      <c r="BL72" s="11"/>
+      <c r="BL72" s="10"/>
       <c r="BN72" t="s">
         <v>828</v>
       </c>
-      <c r="BO72" s="6">
+      <c r="BO72" s="5">
         <v>200000</v>
       </c>
-      <c r="BP72" s="8" t="s">
+      <c r="BP72" s="7" t="s">
         <v>1533</v>
       </c>
-      <c r="BR72" s="8" t="s">
-        <v>1580</v>
+      <c r="BR72" s="7" t="s">
+        <v>1579</v>
       </c>
     </row>
-    <row r="73" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C73" s="18" t="s">
+    <row r="73" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C73" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="15" t="s">
         <v>521</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="F73" s="18" t="s">
+      <c r="F73" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="G73" s="18" t="s">
+      <c r="G73" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="H73" s="18" t="s">
+      <c r="H73" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="I73" s="18" t="s">
+      <c r="I73" s="15" t="s">
         <v>524</v>
       </c>
-      <c r="J73" s="18" t="s">
+      <c r="J73" s="15" t="s">
         <v>525</v>
       </c>
-      <c r="K73" s="18" t="s">
+      <c r="K73" s="15" t="s">
         <v>526</v>
       </c>
-      <c r="L73" s="18" t="s">
+      <c r="L73" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="M73" s="18" t="s">
+      <c r="M73" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="N73" s="18" t="s">
+      <c r="N73" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="O73" s="18" t="s">
+      <c r="O73" s="15" t="s">
         <v>528</v>
       </c>
-      <c r="P73" s="18" t="s">
+      <c r="P73" s="15" t="s">
         <v>488</v>
       </c>
-      <c r="Q73" s="18" t="s">
+      <c r="Q73" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="R73" s="18" t="s">
+      <c r="R73" s="15" t="s">
         <v>530</v>
       </c>
-      <c r="S73" s="18" t="s">
+      <c r="S73" s="15" t="s">
         <v>531</v>
       </c>
-      <c r="T73" s="18"/>
-      <c r="U73" s="18" t="s">
+      <c r="T73" s="15"/>
+      <c r="U73" s="15" t="s">
         <v>532</v>
       </c>
-      <c r="V73" s="18" t="s">
+      <c r="V73" s="15" t="s">
         <v>533</v>
       </c>
-      <c r="W73" s="18" t="s">
+      <c r="W73" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="X73" s="18" t="s">
+      <c r="X73" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="Y73" s="19" t="s">
+      <c r="Y73" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="Z73" s="19" t="s">
+      <c r="Z73" s="16" t="s">
         <v>535</v>
       </c>
-      <c r="AA73" s="18" t="s">
+      <c r="AA73" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="AB73" s="18" t="s">
+      <c r="AB73" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="AC73" s="18" t="s">
+      <c r="AC73" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="AD73" s="19" t="s">
+      <c r="AD73" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="AE73" s="18" t="s">
+      <c r="AE73" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="AF73" s="18" t="s">
+      <c r="AF73" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="AG73" s="19" t="s">
+      <c r="AG73" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="AH73" s="19" t="s">
+      <c r="AH73" s="16" t="s">
         <v>539</v>
       </c>
-      <c r="AI73" s="19" t="s">
+      <c r="AI73" s="16" t="s">
         <v>540</v>
       </c>
-      <c r="AJ73" s="18" t="s">
+      <c r="AJ73" s="15" t="s">
         <v>541</v>
       </c>
-      <c r="AK73" s="19" t="s">
+      <c r="AK73" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="AL73" s="19" t="s">
+      <c r="AL73" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="AM73" s="19" t="s">
+      <c r="AM73" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="AN73" s="19" t="s">
+      <c r="AN73" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="AO73" s="19" t="s">
+      <c r="AO73" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="AP73" s="18" t="s">
+      <c r="AP73" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AQ73" s="18" t="s">
+      <c r="AQ73" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="AR73" s="18" t="s">
+      <c r="AR73" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AS73" s="18" t="s">
+      <c r="AS73" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AT73" s="18"/>
-      <c r="AU73" s="18"/>
-      <c r="AV73" s="18" t="s">
+      <c r="AT73" s="15"/>
+      <c r="AU73" s="15"/>
+      <c r="AV73" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AW73" s="18" t="s">
+      <c r="AW73" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AX73" s="18" t="s">
+      <c r="AX73" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="AY73" s="18" t="s">
+      <c r="AY73" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AZ73" s="18"/>
-      <c r="BA73" s="18"/>
-      <c r="BB73" s="18"/>
-      <c r="BC73" s="18"/>
-      <c r="BD73" s="19" t="s">
+      <c r="AZ73" s="15"/>
+      <c r="BA73" s="15"/>
+      <c r="BB73" s="15"/>
+      <c r="BC73" s="15"/>
+      <c r="BD73" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="BE73" s="18" t="s">
+      <c r="BE73" s="15" t="s">
         <v>548</v>
       </c>
-      <c r="BF73" s="19" t="s">
+      <c r="BF73" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="BG73" s="19" t="s">
+      <c r="BG73" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="BH73" s="18" t="s">
+      <c r="BH73" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="BI73" s="19" t="s">
+      <c r="BI73" s="16" t="s">
         <v>549</v>
       </c>
-      <c r="BJ73" s="18"/>
-      <c r="BK73" s="18" t="s">
+      <c r="BJ73" s="15"/>
+      <c r="BK73" s="15" t="s">
         <v>550</v>
       </c>
-      <c r="BL73" s="18"/>
-      <c r="BM73" s="18" t="s">
+      <c r="BL73" s="15"/>
+      <c r="BM73" s="15" t="s">
         <v>1517</v>
       </c>
-      <c r="BN73" s="18" t="s">
+      <c r="BN73" s="15" t="s">
         <v>1517</v>
       </c>
-      <c r="BO73" s="20">
+      <c r="BO73" s="17">
         <v>200000</v>
       </c>
-      <c r="BP73" s="17" t="s">
+      <c r="BP73" s="14" t="s">
         <v>537</v>
       </c>
-      <c r="BQ73" s="18" t="s">
+      <c r="BQ73" s="15" t="s">
         <v>1541</v>
       </c>
-      <c r="BR73" s="17" t="s">
-        <v>1582</v>
+      <c r="BR73" s="14" t="s">
+        <v>1581</v>
       </c>
     </row>
-    <row r="74" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" t="s">
         <v>973</v>
       </c>
@@ -18377,370 +18375,370 @@
       <c r="BN74" t="s">
         <v>1003</v>
       </c>
-      <c r="BO74" s="6">
+      <c r="BO74" s="5">
         <v>75000</v>
       </c>
-      <c r="BP74" s="8" t="s">
+      <c r="BP74" s="7" t="s">
         <v>1535</v>
       </c>
       <c r="BQ74" t="s">
         <v>1541</v>
       </c>
-      <c r="BR74" s="8" t="s">
+      <c r="BR74" s="7" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="75" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="J75" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="L75" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="M75" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="N75" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="O75" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="P75" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q75" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="R75" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="S75" s="15" t="s">
+        <v>551</v>
+      </c>
+      <c r="T75" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="U75" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="V75" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="W75" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="X75" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="Y75" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="Z75" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="AA75" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="AB75" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AC75" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD75" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="AE75" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="AF75" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG75" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="AH75" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="AI75" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="AJ75" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="AK75" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="AL75" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="AM75" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="AN75" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="AO75" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="AP75" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ75" s="15"/>
+      <c r="AR75" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS75" s="15"/>
+      <c r="AT75" s="15"/>
+      <c r="AU75" s="15"/>
+      <c r="AV75" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW75" s="15"/>
+      <c r="AX75" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="AY75" s="15"/>
+      <c r="AZ75" s="15"/>
+      <c r="BA75" s="15"/>
+      <c r="BB75" s="15"/>
+      <c r="BC75" s="15"/>
+      <c r="BD75" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="BE75" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="BF75" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="BG75" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="BH75" s="15" t="s">
+        <v>582</v>
+      </c>
+      <c r="BI75" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="BJ75" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="BK75" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="BL75" s="15"/>
+      <c r="BM75" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="BN75" s="15" t="s">
+        <v>1517</v>
+      </c>
+      <c r="BO75" s="17">
+        <v>200000</v>
+      </c>
+      <c r="BP75" s="14" t="s">
+        <v>1535</v>
+      </c>
+      <c r="BQ75" s="15"/>
+      <c r="BR75" s="14" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="76" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C76" s="7" t="s">
+        <v>1560</v>
+      </c>
+      <c r="AD76" s="10" t="s">
+        <v>1561</v>
+      </c>
+      <c r="AF76" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="BN76" s="7" t="s">
+        <v>1562</v>
+      </c>
+      <c r="BO76" s="5">
+        <v>30000</v>
+      </c>
+      <c r="BP76" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="BR76" s="7" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="77" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="15"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="14" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="15"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15"/>
+      <c r="L77" s="15"/>
+      <c r="M77" s="15"/>
+      <c r="N77" s="15"/>
+      <c r="O77" s="15"/>
+      <c r="P77" s="15"/>
+      <c r="Q77" s="15"/>
+      <c r="R77" s="15"/>
+      <c r="S77" s="15"/>
+      <c r="T77" s="15"/>
+      <c r="U77" s="15"/>
+      <c r="V77" s="15"/>
+      <c r="W77" s="15"/>
+      <c r="X77" s="15"/>
+      <c r="Y77" s="15"/>
+      <c r="Z77" s="15"/>
+      <c r="AA77" s="15"/>
+      <c r="AB77" s="15"/>
+      <c r="AC77" s="15"/>
+      <c r="AD77" s="15"/>
+      <c r="AE77" s="15"/>
+      <c r="AF77" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG77" s="15"/>
+      <c r="AH77" s="15"/>
+      <c r="AI77" s="15"/>
+      <c r="AJ77" s="15"/>
+      <c r="AK77" s="15"/>
+      <c r="AL77" s="15"/>
+      <c r="AM77" s="15"/>
+      <c r="AN77" s="15"/>
+      <c r="AO77" s="15"/>
+      <c r="AP77" s="15"/>
+      <c r="AQ77" s="15"/>
+      <c r="AR77" s="15"/>
+      <c r="AS77" s="15"/>
+      <c r="AT77" s="15"/>
+      <c r="AU77" s="15"/>
+      <c r="AV77" s="15"/>
+      <c r="AW77" s="15"/>
+      <c r="AX77" s="15"/>
+      <c r="AY77" s="15"/>
+      <c r="AZ77" s="15"/>
+      <c r="BA77" s="15"/>
+      <c r="BB77" s="15"/>
+      <c r="BC77" s="15"/>
+      <c r="BD77" s="15"/>
+      <c r="BE77" s="15"/>
+      <c r="BF77" s="15"/>
+      <c r="BG77" s="15"/>
+      <c r="BH77" s="15"/>
+      <c r="BI77" s="15"/>
+      <c r="BJ77" s="15"/>
+      <c r="BK77" s="15"/>
+      <c r="BL77" s="15"/>
+      <c r="BM77" s="15"/>
+      <c r="BN77" s="14" t="s">
+        <v>1567</v>
+      </c>
+      <c r="BO77" s="17">
+        <v>50000</v>
+      </c>
+      <c r="BP77" s="14" t="s">
         <v>1580</v>
       </c>
+      <c r="BQ77" s="15"/>
+      <c r="BR77" s="14" t="s">
+        <v>1579</v>
+      </c>
     </row>
-    <row r="75" spans="1:70" s="15" customFormat="1" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C75" s="18" t="s">
-        <v>552</v>
-      </c>
-      <c r="D75" s="18" t="s">
-        <v>553</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>554</v>
-      </c>
-      <c r="F75" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="G75" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="H75" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I75" s="18" t="s">
-        <v>524</v>
-      </c>
-      <c r="J75" s="18" t="s">
-        <v>556</v>
-      </c>
-      <c r="K75" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="L75" s="18" t="s">
-        <v>558</v>
-      </c>
-      <c r="M75" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="N75" s="18" t="s">
-        <v>559</v>
-      </c>
-      <c r="O75" s="18" t="s">
-        <v>560</v>
-      </c>
-      <c r="P75" s="18" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q75" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="R75" s="18" t="s">
-        <v>563</v>
-      </c>
-      <c r="S75" s="18" t="s">
-        <v>551</v>
-      </c>
-      <c r="T75" s="18" t="s">
-        <v>564</v>
-      </c>
-      <c r="U75" s="18" t="s">
-        <v>565</v>
-      </c>
-      <c r="V75" s="18" t="s">
-        <v>566</v>
-      </c>
-      <c r="W75" s="18" t="s">
-        <v>567</v>
-      </c>
-      <c r="X75" s="18" t="s">
-        <v>568</v>
-      </c>
-      <c r="Y75" s="19" t="s">
-        <v>569</v>
-      </c>
-      <c r="Z75" s="19" t="s">
-        <v>570</v>
-      </c>
-      <c r="AA75" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="AB75" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="AC75" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="AD75" s="19" t="s">
-        <v>571</v>
-      </c>
-      <c r="AE75" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="AF75" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="AG75" s="19" t="s">
-        <v>572</v>
-      </c>
-      <c r="AH75" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="AI75" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="AJ75" s="19" t="s">
-        <v>575</v>
-      </c>
-      <c r="AK75" s="19" t="s">
-        <v>576</v>
-      </c>
-      <c r="AL75" s="19" t="s">
-        <v>577</v>
-      </c>
-      <c r="AM75" s="19" t="s">
-        <v>578</v>
-      </c>
-      <c r="AN75" s="19" t="s">
-        <v>579</v>
-      </c>
-      <c r="AO75" s="19" t="s">
-        <v>580</v>
-      </c>
-      <c r="AP75" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ75" s="18"/>
-      <c r="AR75" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AS75" s="18"/>
-      <c r="AT75" s="18"/>
-      <c r="AU75" s="18"/>
-      <c r="AV75" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AW75" s="18"/>
-      <c r="AX75" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AY75" s="18"/>
-      <c r="AZ75" s="18"/>
-      <c r="BA75" s="18"/>
-      <c r="BB75" s="18"/>
-      <c r="BC75" s="18"/>
-      <c r="BD75" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="BE75" s="18" t="s">
-        <v>581</v>
-      </c>
-      <c r="BF75" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="BG75" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="BH75" s="18" t="s">
-        <v>582</v>
-      </c>
-      <c r="BI75" s="19" t="s">
-        <v>583</v>
-      </c>
-      <c r="BJ75" s="18" t="s">
-        <v>584</v>
-      </c>
-      <c r="BK75" s="18" t="s">
-        <v>585</v>
-      </c>
-      <c r="BL75" s="18"/>
-      <c r="BM75" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="BN75" s="18" t="s">
+    <row r="78" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C78" s="7" t="s">
+        <v>1554</v>
+      </c>
+      <c r="AF78" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="BN78" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="BO78" s="5">
+        <v>50000</v>
+      </c>
+      <c r="BP78" s="7" t="s">
+        <v>1580</v>
+      </c>
+      <c r="BR78" s="7" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="79" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C79" s="7" t="s">
+        <v>1573</v>
+      </c>
+      <c r="AF79" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="BN79" s="7" t="s">
         <v>1517</v>
       </c>
-      <c r="BO75" s="20">
-        <v>200000</v>
-      </c>
-      <c r="BP75" s="17" t="s">
+      <c r="BO79" s="5">
+        <v>50000</v>
+      </c>
+      <c r="BP79" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="BR79" s="7" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="80" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF80" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="BN80" s="7" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BO80" s="5">
+        <v>25000</v>
+      </c>
+      <c r="BP80" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="BQ75" s="18"/>
-      <c r="BR75" s="17" t="s">
-        <v>1582</v>
+      <c r="BR80" s="7" t="s">
+        <v>1594</v>
       </c>
     </row>
-    <row r="76" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="8" t="s">
-        <v>1561</v>
-      </c>
-      <c r="AD76" s="11" t="s">
-        <v>1562</v>
-      </c>
-      <c r="AF76" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="BN76" s="8" t="s">
-        <v>1563</v>
-      </c>
-      <c r="BO76" s="6">
-        <v>30000</v>
-      </c>
-      <c r="BP76" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="BR76" s="16" t="s">
-        <v>1582</v>
-      </c>
-    </row>
-    <row r="77" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="18"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="17" t="s">
-        <v>1567</v>
-      </c>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
-      <c r="M77" s="18"/>
-      <c r="N77" s="18"/>
-      <c r="O77" s="18"/>
-      <c r="P77" s="18"/>
-      <c r="Q77" s="18"/>
-      <c r="R77" s="18"/>
-      <c r="S77" s="18"/>
-      <c r="T77" s="18"/>
-      <c r="U77" s="18"/>
-      <c r="V77" s="18"/>
-      <c r="W77" s="18"/>
-      <c r="X77" s="18"/>
-      <c r="Y77" s="18"/>
-      <c r="Z77" s="18"/>
-      <c r="AA77" s="18"/>
-      <c r="AB77" s="18"/>
-      <c r="AC77" s="18"/>
-      <c r="AD77" s="18"/>
-      <c r="AE77" s="18"/>
-      <c r="AF77" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG77" s="18"/>
-      <c r="AH77" s="18"/>
-      <c r="AI77" s="18"/>
-      <c r="AJ77" s="18"/>
-      <c r="AK77" s="18"/>
-      <c r="AL77" s="18"/>
-      <c r="AM77" s="18"/>
-      <c r="AN77" s="18"/>
-      <c r="AO77" s="18"/>
-      <c r="AP77" s="18"/>
-      <c r="AQ77" s="18"/>
-      <c r="AR77" s="18"/>
-      <c r="AS77" s="18"/>
-      <c r="AT77" s="18"/>
-      <c r="AU77" s="18"/>
-      <c r="AV77" s="18"/>
-      <c r="AW77" s="18"/>
-      <c r="AX77" s="18"/>
-      <c r="AY77" s="18"/>
-      <c r="AZ77" s="18"/>
-      <c r="BA77" s="18"/>
-      <c r="BB77" s="18"/>
-      <c r="BC77" s="18"/>
-      <c r="BD77" s="18"/>
-      <c r="BE77" s="18"/>
-      <c r="BF77" s="18"/>
-      <c r="BG77" s="18"/>
-      <c r="BH77" s="18"/>
-      <c r="BI77" s="18"/>
-      <c r="BJ77" s="18"/>
-      <c r="BK77" s="18"/>
-      <c r="BL77" s="18"/>
-      <c r="BM77" s="18"/>
-      <c r="BN77" s="17" t="s">
-        <v>1568</v>
-      </c>
-      <c r="BO77" s="20">
-        <v>50000</v>
-      </c>
-      <c r="BP77" s="17" t="s">
-        <v>1581</v>
-      </c>
-      <c r="BQ77" s="18"/>
-      <c r="BR77" s="17" t="s">
-        <v>1580</v>
-      </c>
-    </row>
-    <row r="78" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C78" s="8" t="s">
-        <v>1554</v>
-      </c>
-      <c r="AF78" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="BN78" s="8" t="s">
-        <v>1568</v>
-      </c>
-      <c r="BO78" s="6">
-        <v>50000</v>
-      </c>
-      <c r="BP78" s="8" t="s">
-        <v>1581</v>
-      </c>
-      <c r="BR78" s="8" t="s">
-        <v>1580</v>
-      </c>
-    </row>
-    <row r="79" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C79" s="8" t="s">
-        <v>1574</v>
-      </c>
-      <c r="AF79" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="BN79" s="8" t="s">
-        <v>1517</v>
-      </c>
-      <c r="BO79" s="6">
-        <v>50000</v>
-      </c>
-      <c r="BP79" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="BR79" s="8" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="80" spans="1:70" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C80" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF80" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="BN80" s="8" t="s">
-        <v>1599</v>
-      </c>
-      <c r="BO80" s="6">
-        <v>25000</v>
-      </c>
-      <c r="BP80" s="8" t="s">
-        <v>1535</v>
-      </c>
-      <c r="BR80" s="8" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="81" spans="67:67" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="BO81" s="6">
+    <row r="81" spans="67:67" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="BO81" s="5">
         <f>SUM(BO2:BO80)</f>
         <v>17085999</v>
       </c>
@@ -18756,17 +18754,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B698FADE-2A54-4D0D-8174-5E09B2BEE041}">
   <dimension ref="A2:BP31"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:68" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:68" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>1174</v>
       </c>
       <c r="B2" t="s">
@@ -18775,41 +18773,41 @@
       <c r="C2" t="s">
         <v>1535</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>250000</v>
       </c>
       <c r="E2" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F2" s="8" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="BM2" s="5"/>
+    </row>
+    <row r="3" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>1586</v>
       </c>
-      <c r="BM2" s="6"/>
-    </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>1587</v>
-      </c>
       <c r="B3" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="C3" t="s">
         <v>1535</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>35000</v>
       </c>
       <c r="E3" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>1586</v>
-      </c>
-      <c r="BM3" s="6"/>
+        <v>1593</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="BM3" s="5"/>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>1600</v>
+    <row r="4" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>1599</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -18817,19 +18815,19 @@
       <c r="C4" t="s">
         <v>1535</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>25000</v>
       </c>
       <c r="E4" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>1586</v>
-      </c>
-      <c r="BM4" s="6"/>
+        <v>1593</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="BM4" s="5"/>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
         <v>61</v>
       </c>
       <c r="B5" t="s">
@@ -18838,20 +18836,20 @@
       <c r="C5" t="s">
         <v>1535</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>25000</v>
       </c>
       <c r="E5" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>1586</v>
-      </c>
-      <c r="BM5" s="6"/>
+        <v>1593</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="BM5" s="5"/>
     </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -18859,39 +18857,39 @@
       <c r="C6" t="s">
         <v>1535</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>10000</v>
       </c>
       <c r="E6" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>1586</v>
+        <v>1593</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>15000</v>
       </c>
       <c r="E7" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>1586</v>
+        <v>1593</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>1585</v>
       </c>
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AD7" s="3"/>
-      <c r="AF7" s="8" t="s">
+      <c r="AF7" s="7" t="s">
         <v>69</v>
       </c>
       <c r="AG7" s="2"/>
@@ -18906,17 +18904,17 @@
       <c r="BG7" s="2"/>
       <c r="BI7" s="2"/>
       <c r="BJ7" s="2"/>
-      <c r="BN7" s="8" t="s">
-        <v>1570</v>
-      </c>
-      <c r="BO7" s="6">
+      <c r="BN7" s="7" t="s">
+        <v>1569</v>
+      </c>
+      <c r="BO7" s="5">
         <v>750000</v>
       </c>
-      <c r="BP7" s="8"/>
+      <c r="BP7" s="7"/>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B8" t="s">
         <v>1546</v>
@@ -18924,19 +18922,19 @@
       <c r="C8" t="s">
         <v>1535</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>100000</v>
       </c>
       <c r="E8" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>1586</v>
+        <v>1593</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
@@ -18944,322 +18942,322 @@
       <c r="C9" t="s">
         <v>1535</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>10000</v>
       </c>
       <c r="E9" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>1586</v>
+        <v>1593</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1592</v>
-      </c>
-      <c r="B10" s="8" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>1535</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>15000</v>
       </c>
       <c r="E10" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>1586</v>
+        <v>1593</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>1585</v>
       </c>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>1593</v>
+      <c r="B11" s="7" t="s">
+        <v>1592</v>
       </c>
       <c r="C11" t="s">
         <v>1535</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>300000</v>
       </c>
       <c r="E11" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>1595</v>
-      </c>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>1590</v>
-      </c>
-      <c r="B12" s="8" t="s">
+    <row r="12" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>1546</v>
       </c>
       <c r="C12" t="s">
         <v>1535</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>100000</v>
       </c>
       <c r="E12" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F12" s="8" t="s">
+    </row>
+    <row r="13" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>1595</v>
       </c>
+      <c r="B13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D13" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>1594</v>
+      </c>
     </row>
-    <row r="13" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>1598</v>
-      </c>
-      <c r="D13" s="6">
-        <v>50000</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>1597</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>1587</v>
+    <row r="14" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>1586</v>
       </c>
       <c r="B14" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="C14" t="s">
         <v>1535</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>35000</v>
       </c>
       <c r="E14" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>1595</v>
-      </c>
     </row>
-    <row r="15" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D15" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
         <v>1600</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="D15" s="6">
-        <v>15000</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D16" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>1595</v>
-      </c>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.35">
-      <c r="A16" s="23" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="21" t="s">
         <v>1601</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D17" s="5">
         <v>10000</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>1595</v>
-      </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="24" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D18" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="21" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D19" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
         <v>1602</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="D17" s="6">
-        <v>10000</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D20" s="5">
+        <v>5300</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>1595</v>
-      </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
-        <v>1588</v>
-      </c>
-      <c r="B18" s="8" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="23" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D21" s="17">
+        <v>5000</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="14" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D22" s="17">
+        <v>4100</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="21" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="D18" s="6">
-        <v>10000</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D23" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>1595</v>
-      </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="24" t="s">
-        <v>1591</v>
-      </c>
-      <c r="B19" s="8" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="20" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>1535</v>
       </c>
-      <c r="D19" s="6">
-        <v>10000</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D24" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>1594</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>1595</v>
-      </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>1603</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D20" s="6">
-        <v>5300</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="26" t="s">
-        <v>1604</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>1598</v>
-      </c>
-      <c r="D21" s="20">
-        <v>5000</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="17" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="26" t="s">
-        <v>1605</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>1598</v>
-      </c>
-      <c r="D22" s="20">
-        <v>4100</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="17" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="24" t="s">
-        <v>1606</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1500</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1500</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D25" s="7">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D25" s="6">
         <f>SUM(D2:D24)</f>
         <v>1042400</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D27" s="22">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D27" s="19">
         <f>SUM(D25+'KIP Grants'!BO81)</f>
         <v>18128399</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D30" s="27">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D30" s="24">
         <v>18078399</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E31" s="22">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E31" s="19">
         <f>SUM(D27-D30)</f>
         <v>50000</v>
       </c>
